--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207C52DF-BDCD-4C84-AE15-979C960BDD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A97C4BA-177B-4B2B-8E6E-87784ADF98B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="137">
   <si>
     <t>Date</t>
   </si>
@@ -324,6 +324,126 @@
   </si>
   <si>
     <t>TAPAHA GAYE</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Supermarché</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vais essayer avec </t>
+  </si>
+  <si>
+    <t>Chocolat transparent 200gx24pcs</t>
+  </si>
+  <si>
+    <t>Korka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mogi deme dh </t>
+  </si>
+  <si>
+    <t>Moustapha  seye</t>
+  </si>
+  <si>
+    <t>Café stick Altimo 1,5gx09boites</t>
+  </si>
+  <si>
+    <t>Pape Mbathie</t>
+  </si>
+  <si>
+    <t>Ras</t>
+  </si>
+  <si>
+    <t>Café pot Refraish 200g</t>
+  </si>
+  <si>
+    <t>DKR Plateau</t>
+  </si>
+  <si>
+    <t>Bacary</t>
+  </si>
+  <si>
+    <t>Ousmane kebe</t>
+  </si>
+  <si>
+    <t>Sidi</t>
+  </si>
+  <si>
+    <t>Problème de localisation</t>
+  </si>
+  <si>
+    <t>Ba boutique</t>
+  </si>
+  <si>
+    <t>Lamine (Loum)</t>
+  </si>
+  <si>
+    <t>Modou</t>
+  </si>
+  <si>
+    <t>Abdou Diop</t>
+  </si>
+  <si>
+    <t>Sicap Mbao</t>
+  </si>
+  <si>
+    <t>CHERIF DIALLO</t>
+  </si>
+  <si>
+    <t>Cowmilk UHT demi écrémé 500ml</t>
+  </si>
+  <si>
+    <t>Baye Modou</t>
+  </si>
+  <si>
+    <t>Chocolat jaune 400g x 12 pcs</t>
+  </si>
+  <si>
+    <t>Cafe au Lait 3-en-1</t>
+  </si>
+  <si>
+    <t>Ouakam</t>
+  </si>
+  <si>
+    <t>Dian Diallo</t>
+  </si>
+  <si>
+    <t>Sonké Global Distribution Suarl</t>
+  </si>
+  <si>
+    <t>NDEYE MARÉME DIOP</t>
+  </si>
+  <si>
+    <t>Moustapha</t>
+  </si>
+  <si>
+    <t>Client non Partenaire</t>
+  </si>
+  <si>
+    <t>Madina</t>
+  </si>
+  <si>
+    <t>Gueule Tapée</t>
+  </si>
+  <si>
+    <t>Souleymane</t>
+  </si>
+  <si>
+    <t>Grand Dakar</t>
+  </si>
+  <si>
+    <t>Aladji</t>
+  </si>
+  <si>
+    <t>MATAR LY</t>
+  </si>
+  <si>
+    <t>Médina</t>
+  </si>
+  <si>
+    <t>Serigne Modou</t>
   </si>
 </sst>
 </file>
@@ -391,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -413,10 +533,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -429,40 +557,15 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <font>
-        <color auto="1"/>
-        <name val="TIMES"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-        <name val="TIMES"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -504,6 +607,20 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+        <name val="TIMES"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -674,6 +791,21 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <color auto="1"/>
+        <name val="TIMES"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
@@ -734,27 +866,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P30" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P30" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P59" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P59" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{72E50CE0-52B1-4C49-9D23-C97154D649A5}" name="zone" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{E26577ED-9647-48EE-BE53-9D2F344CB36B}" name="secteur" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{43164A48-AFB0-417D-94C4-5347A67ACD14}" name="Nom_du_magasin" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{66D926A0-8C65-4D89-BA92-AA9653C7DE06}" name="Telephone_Client" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{8D4D921E-310A-44FC-AA1D-F30B627C5984}" name="Type" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{636AF8A9-C9D0-49B6-94C8-FFB87B44FA47}" name="Point_de_Vente" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{35E41B20-D7EB-4025-A9CC-62B85956ABCD}" name="Operation" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{AB905DE1-CC5E-4C11-8318-9C04B6D96EC3}" name="Commentaire" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{9BC88C3B-EEBD-4156-81CB-075746F3F057}" name="Produit" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{8DD706C4-BCF7-47C0-9913-F482F7A2F321}" name="Quantites" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{D96EE09E-B22B-4D75-AABE-AEBF7CE286A6}" name="Prix_Unitaire" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{B1727D51-96B6-4015-83C5-EBCAD96E9834}" name="Prix Total" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{72E50CE0-52B1-4C49-9D23-C97154D649A5}" name="zone" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{E26577ED-9647-48EE-BE53-9D2F344CB36B}" name="secteur" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{43164A48-AFB0-417D-94C4-5347A67ACD14}" name="Nom_du_magasin" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{66D926A0-8C65-4D89-BA92-AA9653C7DE06}" name="Telephone_Client" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{8D4D921E-310A-44FC-AA1D-F30B627C5984}" name="Type" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{636AF8A9-C9D0-49B6-94C8-FFB87B44FA47}" name="Point_de_Vente" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{35E41B20-D7EB-4025-A9CC-62B85956ABCD}" name="Operation" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{AB905DE1-CC5E-4C11-8318-9C04B6D96EC3}" name="Commentaire" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{9BC88C3B-EEBD-4156-81CB-075746F3F057}" name="Produit" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{8DD706C4-BCF7-47C0-9913-F482F7A2F321}" name="Quantites" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{D96EE09E-B22B-4D75-AABE-AEBF7CE286A6}" name="Prix_Unitaire" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{B1727D51-96B6-4015-83C5-EBCAD96E9834}" name="Prix Total" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="1">
       <calculatedColumnFormula>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="2">
+    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="0">
       <calculatedColumnFormula>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1048,7 +1180,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -1161,11 +1293,11 @@
       <c r="N2">
         <v>450000</v>
       </c>
-      <c r="O2" s="9" t="str">
+      <c r="O2" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P2" s="10" t="str">
+      <c r="P2" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
@@ -1213,1409 +1345,2909 @@
       <c r="N3">
         <v>180000</v>
       </c>
-      <c r="O3" s="9" t="str">
+      <c r="O3" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P3" s="10" t="str">
+      <c r="P3" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A4" s="11">
+      <c r="A4" s="9">
         <v>46269</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <v>784227996</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="12" t="s">
+      <c r="G4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="10">
         <v>25</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="12">
         <v>26000</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="12">
         <v>650000</v>
       </c>
-      <c r="O4" s="9" t="str">
+      <c r="O4" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P4" s="10" t="str">
+      <c r="P4" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A5" s="11">
+      <c r="A5" s="9">
         <v>46268</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="11">
         <v>777802399</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="12" t="s">
+      <c r="H5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="10">
         <v>2</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="12">
         <v>11500</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="12">
         <v>23000</v>
       </c>
-      <c r="O5" s="9" t="str">
+      <c r="O5" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P5" s="10" t="str">
+      <c r="P5" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A6" s="11">
+      <c r="A6" s="9">
         <v>46268</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <v>777802399</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="12" t="s">
+      <c r="H6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="10">
         <v>1</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="12">
         <v>9000</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="12">
         <v>9000</v>
       </c>
-      <c r="O6" s="9" t="str">
+      <c r="O6" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P6" s="10" t="str">
+      <c r="P6" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A7" s="11">
+      <c r="A7" s="9">
         <v>46268</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="11">
         <v>766447275</v>
       </c>
-      <c r="G7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="12" t="s">
+      <c r="G7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="10">
         <v>25</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="12">
         <v>9000</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="12">
         <v>225000</v>
       </c>
-      <c r="O7" s="9" t="str">
+      <c r="O7" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P7" s="10" t="str">
+      <c r="P7" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A8" s="11">
+      <c r="A8" s="9">
         <v>46267</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="11">
         <v>776317469</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="12" t="s">
+      <c r="G8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="10">
         <v>25</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="12">
         <v>11250</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="12">
         <v>281250</v>
       </c>
-      <c r="O8" s="9" t="str">
+      <c r="O8" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P8" s="10" t="str">
+      <c r="P8" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A9" s="11">
+      <c r="A9" s="9">
         <v>46267</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="11">
         <v>783740441</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="12" t="s">
+      <c r="G9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="10">
         <v>1</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="12">
         <v>15000</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="12">
         <v>15000</v>
       </c>
-      <c r="O9" s="9" t="str">
+      <c r="O9" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P9" s="10" t="str">
+      <c r="P9" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A10" s="11">
+      <c r="A10" s="9">
         <v>46267</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="11">
         <v>783740441</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="12" t="s">
+      <c r="G10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="10">
         <v>2</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="12">
         <v>15500</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="12">
         <v>31000</v>
       </c>
-      <c r="O10" s="9" t="str">
+      <c r="O10" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P10" s="10" t="str">
+      <c r="P10" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A11" s="11">
+      <c r="A11" s="9">
         <v>46267</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="11">
         <v>783740441</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="12" t="s">
+      <c r="G11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="10">
         <v>3</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="12">
         <v>11250</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="12">
         <v>33750</v>
       </c>
-      <c r="O11" s="9" t="str">
+      <c r="O11" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P11" s="10" t="str">
+      <c r="P11" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A12" s="11">
+      <c r="A12" s="9">
         <v>46267</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="11">
         <v>704738232</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="12" t="s">
+      <c r="H12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="10">
         <v>2</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="12">
         <v>11250</v>
       </c>
-      <c r="N12" s="14">
+      <c r="N12" s="12">
         <v>22500</v>
       </c>
-      <c r="O12" s="9" t="str">
+      <c r="O12" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P12" s="10" t="str">
+      <c r="P12" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A13" s="11">
+      <c r="A13" s="9">
         <v>46267</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="11">
         <v>704738232</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="12" t="s">
+      <c r="H13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="10">
         <v>1</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="12">
         <v>15000</v>
       </c>
-      <c r="N13" s="14">
+      <c r="N13" s="12">
         <v>15000</v>
       </c>
-      <c r="O13" s="9" t="str">
+      <c r="O13" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P13" s="10" t="str">
+      <c r="P13" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A14" s="11">
+      <c r="A14" s="9">
         <v>46266</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="11">
         <v>783758073</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="12" t="s">
+      <c r="G14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="10">
         <v>25</v>
       </c>
-      <c r="M14" s="14">
+      <c r="M14" s="12">
         <v>26000</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="12">
         <v>650000</v>
       </c>
-      <c r="O14" s="9" t="str">
+      <c r="O14" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P14" s="10" t="str">
+      <c r="P14" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A15" s="11">
+      <c r="A15" s="9">
         <v>46266</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="11">
         <v>778657940</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="12" t="s">
+      <c r="G15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="K15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="10">
         <v>25</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="12">
         <v>26000</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="12">
         <v>650000</v>
       </c>
-      <c r="O15" s="9" t="str">
+      <c r="O15" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P15" s="10" t="str">
+      <c r="P15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A16" s="11">
+      <c r="A16" s="9">
         <v>46266</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="11">
         <v>784494590</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="12" t="s">
+      <c r="G16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="10">
         <v>30</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M16" s="12">
         <v>9000</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="12">
         <v>270000</v>
       </c>
-      <c r="O16" s="9" t="str">
+      <c r="O16" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P16" s="10" t="str">
+      <c r="P16" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A17" s="11">
+      <c r="A17" s="9">
         <v>46266</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="11">
         <v>777643068</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="12" t="s">
+      <c r="G17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="12" t="s">
+      <c r="K17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="10">
         <v>20</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="12">
         <v>9000</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="12">
         <v>180000</v>
       </c>
-      <c r="O17" s="9" t="str">
+      <c r="O17" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P17" s="10" t="str">
+      <c r="P17" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A18" s="11">
+      <c r="A18" s="9">
         <v>46266</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="11">
         <v>773122246</v>
       </c>
-      <c r="G18" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="12" t="s">
+      <c r="G18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="K18" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="10">
         <v>25</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="12">
         <v>26000</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="12">
         <v>650000</v>
       </c>
-      <c r="O18" s="9" t="str">
+      <c r="O18" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P18" s="10" t="str">
+      <c r="P18" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A19" s="11">
+      <c r="A19" s="9">
         <v>46266</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="11">
         <v>774993694</v>
       </c>
-      <c r="G19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="12" t="s">
+      <c r="G19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="K19" s="12" t="s">
+      <c r="K19" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="10">
         <v>100</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="12">
         <v>26000</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="12">
         <v>2600000</v>
       </c>
-      <c r="O19" s="9" t="str">
+      <c r="O19" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P19" s="10" t="str">
+      <c r="P19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A20" s="11">
+      <c r="A20" s="9">
         <v>46266</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="11">
         <v>771985160</v>
       </c>
-      <c r="G20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="12" t="s">
+      <c r="G20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="10">
         <v>100</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="12">
         <v>26000</v>
       </c>
-      <c r="N20" s="14">
+      <c r="N20" s="12">
         <v>2600000</v>
       </c>
-      <c r="O20" s="9" t="str">
+      <c r="O20" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P20" s="10" t="str">
+      <c r="P20" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A21" s="11">
+      <c r="A21" s="9">
         <v>46266</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="11">
         <v>777847210</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="12" t="s">
+      <c r="G21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="10">
         <v>25</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="12">
         <v>9000</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="12">
         <v>225000</v>
       </c>
-      <c r="O21" s="9" t="str">
+      <c r="O21" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P21" s="10" t="str">
+      <c r="P21" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A22" s="11">
+      <c r="A22" s="9">
         <v>46269</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="11">
         <v>776536527</v>
       </c>
-      <c r="G22" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="12" t="s">
+      <c r="G22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="10">
         <v>20</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="12">
         <v>9000</v>
       </c>
-      <c r="N22" s="14">
+      <c r="N22" s="12">
         <v>180000</v>
       </c>
-      <c r="O22" s="9" t="str">
+      <c r="O22" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P22" s="10" t="str">
+      <c r="P22" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A23" s="11">
+      <c r="A23" s="9">
         <v>46269</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="11">
         <v>776536527</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="12" t="s">
+      <c r="G23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="K23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="10">
         <v>10</v>
       </c>
-      <c r="M23" s="14">
+      <c r="M23" s="12">
         <v>9000</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="12">
         <v>90000</v>
       </c>
-      <c r="O23" s="9" t="str">
+      <c r="O23" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P23" s="10" t="str">
+      <c r="P23" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A24" s="11">
+      <c r="A24" s="9">
         <v>46268</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="11">
         <v>770933492</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="12" t="s">
+      <c r="G24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="K24" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="10">
         <v>30</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M24" s="12">
         <v>9000</v>
       </c>
-      <c r="N24" s="14">
+      <c r="N24" s="12">
         <v>270000</v>
       </c>
-      <c r="O24" s="9" t="str">
+      <c r="O24" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P24" s="10" t="str">
+      <c r="P24" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A25" s="11">
+      <c r="A25" s="9">
         <v>46268</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="11">
         <v>770933492</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="12" t="s">
+      <c r="G25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="K25" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="10">
         <v>1</v>
       </c>
-      <c r="M25" s="14">
+      <c r="M25" s="12">
         <v>6500</v>
       </c>
-      <c r="N25" s="14">
+      <c r="N25" s="12">
         <v>6500</v>
       </c>
-      <c r="O25" s="9" t="str">
+      <c r="O25" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P25" s="10" t="str">
+      <c r="P25" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A26" s="11">
+      <c r="A26" s="9">
         <v>46268</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="11">
         <v>781282357</v>
       </c>
-      <c r="G26" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12" t="s">
+      <c r="G26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="10">
         <v>100</v>
       </c>
-      <c r="M26" s="14">
+      <c r="M26" s="12">
         <v>26000</v>
       </c>
-      <c r="N26" s="14">
+      <c r="N26" s="12">
         <v>2600000</v>
       </c>
-      <c r="O26" s="9" t="str">
+      <c r="O26" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P26" s="10" t="str">
+      <c r="P26" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A27" s="11">
+      <c r="A27" s="9">
         <v>46268</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="11">
         <v>784537895</v>
       </c>
-      <c r="G27" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12" t="s">
+      <c r="G27" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="10">
         <v>100</v>
       </c>
-      <c r="M27" s="14">
+      <c r="M27" s="12">
         <v>9000</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="12">
         <v>900000</v>
       </c>
-      <c r="O27" s="9" t="str">
+      <c r="O27" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P27" s="10" t="str">
+      <c r="P27" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A28" s="11">
+      <c r="A28" s="9">
         <v>46268</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="11">
         <v>776428218</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12" t="s">
+      <c r="H28" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L28" s="12">
+      <c r="L28" s="10">
         <v>50</v>
       </c>
-      <c r="M28" s="14">
+      <c r="M28" s="12">
         <v>6500</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="12">
         <v>325000</v>
       </c>
-      <c r="O28" s="9" t="str">
+      <c r="O28" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P28" s="10" t="str">
+      <c r="P28" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A29" s="11">
+      <c r="A29" s="9">
         <v>46267</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="11">
         <v>774216339</v>
       </c>
-      <c r="G29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="12" t="s">
+      <c r="G29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K29" s="12" t="s">
+      <c r="K29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="10">
         <v>2</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="12">
         <v>28000</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="12">
         <v>56000</v>
       </c>
-      <c r="O29" s="9" t="str">
+      <c r="O29" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P29" s="10" t="str">
+      <c r="P29" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A30" s="11">
+      <c r="A30" s="9">
         <v>46267</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="11">
         <v>774216339</v>
       </c>
-      <c r="G30" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="12" t="s">
+      <c r="G30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K30" s="12" t="s">
+      <c r="K30" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="10">
         <v>25</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="12">
         <v>26000</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="12">
         <v>650000</v>
       </c>
-      <c r="O30" s="9" t="str">
+      <c r="O30" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S36</v>
       </c>
-      <c r="P30" s="10" t="str">
+      <c r="P30" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A31" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="15">
+        <v>778420348</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L31" s="14">
+        <v>1</v>
+      </c>
+      <c r="M31" s="16">
+        <v>12500</v>
+      </c>
+      <c r="N31" s="16">
+        <v>12500</v>
+      </c>
+      <c r="O31" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P31" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A32" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="15">
+        <v>772131614</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" s="14">
+        <v>10</v>
+      </c>
+      <c r="M32" s="16">
+        <v>9000</v>
+      </c>
+      <c r="N32" s="16">
+        <v>90000</v>
+      </c>
+      <c r="O32" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P32" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A33" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="15">
+        <v>775630094</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="L33" s="14">
+        <v>25</v>
+      </c>
+      <c r="M33" s="16">
+        <v>28000</v>
+      </c>
+      <c r="N33" s="16">
+        <v>700000</v>
+      </c>
+      <c r="O33" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P33" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A34" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="15">
+        <v>771471771</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L34" s="14">
+        <v>10</v>
+      </c>
+      <c r="M34" s="16">
+        <v>19500</v>
+      </c>
+      <c r="N34" s="16">
+        <v>195000</v>
+      </c>
+      <c r="O34" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P34" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="15">
+        <v>771471771</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" s="14">
+        <v>10</v>
+      </c>
+      <c r="M35" s="16">
+        <v>11250</v>
+      </c>
+      <c r="N35" s="16">
+        <v>112500</v>
+      </c>
+      <c r="O35" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P35" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A36" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F36" s="15">
+        <v>770158721</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L36" s="14">
+        <v>150</v>
+      </c>
+      <c r="M36" s="16">
+        <v>6250</v>
+      </c>
+      <c r="N36" s="16">
+        <v>937500</v>
+      </c>
+      <c r="O36" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P36" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A37" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="15">
+        <v>775044214</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L37" s="14">
+        <v>100</v>
+      </c>
+      <c r="M37" s="16">
+        <v>6250</v>
+      </c>
+      <c r="N37" s="16">
+        <v>625000</v>
+      </c>
+      <c r="O37" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P37" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" s="15">
+        <v>783942599</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" s="14">
+        <v>25</v>
+      </c>
+      <c r="M38" s="16">
+        <v>9000</v>
+      </c>
+      <c r="N38" s="16">
+        <v>225000</v>
+      </c>
+      <c r="O38" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P38" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A39" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="15">
+        <v>777638400</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L39" s="14">
+        <v>2</v>
+      </c>
+      <c r="M39" s="16">
+        <v>15500</v>
+      </c>
+      <c r="N39" s="16">
+        <v>31000</v>
+      </c>
+      <c r="O39" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P39" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A40" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F40" s="15">
+        <v>763578834</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L40" s="14">
+        <v>25</v>
+      </c>
+      <c r="M40" s="16">
+        <v>11250</v>
+      </c>
+      <c r="N40" s="16">
+        <v>281250</v>
+      </c>
+      <c r="O40" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P40" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A41" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="15">
+        <v>774333344</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L41" s="14">
+        <v>5</v>
+      </c>
+      <c r="M41" s="16">
+        <v>6500</v>
+      </c>
+      <c r="N41" s="16">
+        <v>32500</v>
+      </c>
+      <c r="O41" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P41" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A42" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" s="15">
+        <v>774216341</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L42" s="14">
+        <v>25</v>
+      </c>
+      <c r="M42" s="16">
+        <v>26000</v>
+      </c>
+      <c r="N42" s="16">
+        <v>650000</v>
+      </c>
+      <c r="O42" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P42" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A43" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="15">
+        <v>779236547</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L43" s="14">
+        <v>25</v>
+      </c>
+      <c r="M43" s="16">
+        <v>6500</v>
+      </c>
+      <c r="N43" s="16">
+        <v>162500</v>
+      </c>
+      <c r="O43" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P43" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A44" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F44" s="15">
+        <v>760169386</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" s="14">
+        <v>100</v>
+      </c>
+      <c r="M44" s="16">
+        <v>9000</v>
+      </c>
+      <c r="N44" s="16">
+        <v>900000</v>
+      </c>
+      <c r="O44" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P44" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A45" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="15">
+        <v>777638400</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="L45" s="14">
+        <v>2</v>
+      </c>
+      <c r="M45" s="16">
+        <v>15500</v>
+      </c>
+      <c r="N45" s="16">
+        <v>31000</v>
+      </c>
+      <c r="O45" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P45" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A46" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F46" s="15">
+        <v>777638400</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L46" s="14">
+        <v>1</v>
+      </c>
+      <c r="M46" s="16">
+        <v>4500</v>
+      </c>
+      <c r="N46" s="16">
+        <v>4500</v>
+      </c>
+      <c r="O46" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P46" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A47" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47" s="15">
+        <v>775398902</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1</v>
+      </c>
+      <c r="M47" s="16">
+        <v>15500</v>
+      </c>
+      <c r="N47" s="16">
+        <v>15500</v>
+      </c>
+      <c r="O47" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P47" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A48" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F48" s="15">
+        <v>775626425</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L48" s="14">
+        <v>1</v>
+      </c>
+      <c r="M48" s="16">
+        <v>15500</v>
+      </c>
+      <c r="N48" s="16">
+        <v>15500</v>
+      </c>
+      <c r="O48" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P48" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A49" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F49" s="15">
+        <v>775541532</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="14">
+        <v>25</v>
+      </c>
+      <c r="M49" s="16">
+        <v>26000</v>
+      </c>
+      <c r="N49" s="16">
+        <v>650000</v>
+      </c>
+      <c r="O49" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P49" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A50" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F50" s="15">
+        <v>781728925</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L50" s="14">
+        <v>25</v>
+      </c>
+      <c r="M50" s="16">
+        <v>6500</v>
+      </c>
+      <c r="N50" s="16">
+        <v>162500</v>
+      </c>
+      <c r="O50" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P50" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A51" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F51" s="15">
+        <v>785459209</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L51" s="14">
+        <v>15</v>
+      </c>
+      <c r="M51" s="16">
+        <v>26000</v>
+      </c>
+      <c r="N51" s="16">
+        <v>390000</v>
+      </c>
+      <c r="O51" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P51" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A52" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="F52" s="15">
+        <v>773366070</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="L52" s="14">
+        <v>10</v>
+      </c>
+      <c r="M52" s="16">
+        <v>28000</v>
+      </c>
+      <c r="N52" s="16">
+        <v>280000</v>
+      </c>
+      <c r="O52" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P52" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A53" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F53" s="15">
+        <v>772377240</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L53" s="14">
+        <v>25</v>
+      </c>
+      <c r="M53" s="16">
+        <v>19500</v>
+      </c>
+      <c r="N53" s="16">
+        <v>487500</v>
+      </c>
+      <c r="O53" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P53" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A54" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="15">
+        <v>774245132</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" s="14">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16">
+        <v>26000</v>
+      </c>
+      <c r="N54" s="16">
+        <v>1300000</v>
+      </c>
+      <c r="O54" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P54" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A55" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" s="15">
+        <v>784537895</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" s="14">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16">
+        <v>26000</v>
+      </c>
+      <c r="N55" s="16">
+        <v>1300000</v>
+      </c>
+      <c r="O55" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P55" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A56" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F56" s="15">
+        <v>773531341</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="14">
+        <v>200</v>
+      </c>
+      <c r="M56" s="16">
+        <v>26000</v>
+      </c>
+      <c r="N56" s="16">
+        <v>5200000</v>
+      </c>
+      <c r="O56" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P56" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A57" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F57" s="15">
+        <v>775661455</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" s="14">
+        <v>25</v>
+      </c>
+      <c r="M57" s="16">
+        <v>26000</v>
+      </c>
+      <c r="N57" s="16">
+        <v>650000</v>
+      </c>
+      <c r="O57" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P57" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A58" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F58" s="15">
+        <v>775661455</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L58" s="14">
+        <v>25</v>
+      </c>
+      <c r="M58" s="16">
+        <v>19500</v>
+      </c>
+      <c r="N58" s="16">
+        <v>487500</v>
+      </c>
+      <c r="O58" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P58" s="18" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A59" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F59" s="15">
+        <v>783758073</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="L59" s="14">
+        <v>25</v>
+      </c>
+      <c r="M59" s="16">
+        <v>28000</v>
+      </c>
+      <c r="N59" s="16">
+        <v>700000</v>
+      </c>
+      <c r="O59" s="17" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S37</v>
+      </c>
+      <c r="P59" s="18" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A97C4BA-177B-4B2B-8E6E-87784ADF98B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44372A2E-0F04-4481-80EA-9F33FD7CA3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="177">
   <si>
     <t>Date</t>
   </si>
@@ -444,6 +444,126 @@
   </si>
   <si>
     <t>Serigne Modou</t>
+  </si>
+  <si>
+    <t>Keur Mbaye Fall</t>
+  </si>
+  <si>
+    <t>Fallou NGOM</t>
+  </si>
+  <si>
+    <t>Ndiol NDIAYE</t>
+  </si>
+  <si>
+    <t>Grand Boutique</t>
+  </si>
+  <si>
+    <t>ABDOU LATIF DIENG</t>
+  </si>
+  <si>
+    <t>Lait Janus 18gx10</t>
+  </si>
+  <si>
+    <t>PA NDIAYE</t>
+  </si>
+  <si>
+    <t>ABDOURAHMANE BA</t>
+  </si>
+  <si>
+    <t>Rufisque</t>
+  </si>
+  <si>
+    <t>Bass</t>
+  </si>
+  <si>
+    <t>Modou boye</t>
+  </si>
+  <si>
+    <t>Golf</t>
+  </si>
+  <si>
+    <t>AMADOU SOW</t>
+  </si>
+  <si>
+    <t>Café stick Altimo 1,5gx18boites</t>
+  </si>
+  <si>
+    <t>SEYDOU TALL</t>
+  </si>
+  <si>
+    <t>S.K.L</t>
+  </si>
+  <si>
+    <t>Dieuppeul Derkle</t>
+  </si>
+  <si>
+    <t>Seydou</t>
+  </si>
+  <si>
+    <t>Castor</t>
+  </si>
+  <si>
+    <t>Pa Sylla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merci </t>
+  </si>
+  <si>
+    <t>Gueye et frère</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
+  </si>
+  <si>
+    <t>Ibrahima Diallo</t>
+  </si>
+  <si>
+    <t>Asse</t>
+  </si>
+  <si>
+    <t>Yéne</t>
+  </si>
+  <si>
+    <t>Moussa kane</t>
+  </si>
+  <si>
+    <t>Il demande de diminuer le prix</t>
+  </si>
+  <si>
+    <t>Ousmane</t>
+  </si>
+  <si>
+    <t>Il veut essayer le produit</t>
+  </si>
+  <si>
+    <t>Alassane</t>
+  </si>
+  <si>
+    <t>Terminus 54</t>
+  </si>
+  <si>
+    <t>Bala</t>
+  </si>
+  <si>
+    <t>Il dit que de l'aider à vendre le jug lido</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livraison </t>
+  </si>
+  <si>
+    <t>Stapro.com SARL n2</t>
+  </si>
+  <si>
+    <t>Il demande de diminuer le prix des produits</t>
+  </si>
+  <si>
+    <t>Ismaïla</t>
+  </si>
+  <si>
+    <t>Serigne Fallou GAYE</t>
   </si>
 </sst>
 </file>
@@ -453,7 +573,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +594,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="TIMES"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="TIMES"/>
     </font>
@@ -511,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -552,6 +677,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -866,8 +997,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P59" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P59" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P104" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P104" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1180,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -2753,1501 +2884,3825 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A31" s="13">
+      <c r="A31" s="9">
         <v>46274</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="11">
         <v>778420348</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="H31" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="14" t="s">
+      <c r="H31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="K31" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="10">
         <v>1</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="12">
         <v>12500</v>
       </c>
-      <c r="N31" s="16">
+      <c r="N31" s="12">
         <v>12500</v>
       </c>
-      <c r="O31" s="17" t="str">
+      <c r="O31" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P31" s="18" t="str">
+      <c r="P31" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A32" s="13">
+      <c r="A32" s="9">
         <v>46274</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="11">
         <v>772131614</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="14" t="s">
+      <c r="G32" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="K32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L32" s="10">
         <v>10</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="12">
         <v>9000</v>
       </c>
-      <c r="N32" s="16">
+      <c r="N32" s="12">
         <v>90000</v>
       </c>
-      <c r="O32" s="17" t="str">
+      <c r="O32" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P32" s="18" t="str">
+      <c r="P32" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A33" s="13">
+      <c r="A33" s="9">
         <v>46274</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="11">
         <v>775630094</v>
       </c>
-      <c r="G33" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="14" t="s">
+      <c r="G33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K33" s="14" t="s">
+      <c r="K33" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="10">
         <v>25</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="12">
         <v>28000</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="12">
         <v>700000</v>
       </c>
-      <c r="O33" s="17" t="str">
+      <c r="O33" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P33" s="18" t="str">
+      <c r="P33" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A34" s="13">
+      <c r="A34" s="9">
         <v>46273</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="11">
         <v>771471771</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="14" t="s">
+      <c r="H34" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K34" s="14" t="s">
+      <c r="K34" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="10">
         <v>10</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="12">
         <v>19500</v>
       </c>
-      <c r="N34" s="16">
+      <c r="N34" s="12">
         <v>195000</v>
       </c>
-      <c r="O34" s="17" t="str">
+      <c r="O34" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P34" s="18" t="str">
+      <c r="P34" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A35" s="13">
+      <c r="A35" s="9">
         <v>46273</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="11">
         <v>771471771</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="G35" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H35" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="14" t="s">
+      <c r="H35" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K35" s="14" t="s">
+      <c r="K35" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L35" s="10">
         <v>10</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="12">
         <v>11250</v>
       </c>
-      <c r="N35" s="16">
+      <c r="N35" s="12">
         <v>112500</v>
       </c>
-      <c r="O35" s="17" t="str">
+      <c r="O35" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P35" s="18" t="str">
+      <c r="P35" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A36" s="13">
+      <c r="A36" s="9">
         <v>46273</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="11">
         <v>770158721</v>
       </c>
-      <c r="G36" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="K36" s="14" t="s">
+      <c r="G36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L36" s="14">
+      <c r="L36" s="10">
         <v>150</v>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="12">
         <v>6250</v>
       </c>
-      <c r="N36" s="16">
+      <c r="N36" s="12">
         <v>937500</v>
       </c>
-      <c r="O36" s="17" t="str">
+      <c r="O36" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P36" s="18" t="str">
+      <c r="P36" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A37" s="13">
+      <c r="A37" s="9">
         <v>46273</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="11">
         <v>775044214</v>
       </c>
-      <c r="G37" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="K37" s="14" t="s">
+      <c r="G37" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L37" s="14">
+      <c r="L37" s="10">
         <v>100</v>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="12">
         <v>6250</v>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="12">
         <v>625000</v>
       </c>
-      <c r="O37" s="17" t="str">
+      <c r="O37" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P37" s="18" t="str">
+      <c r="P37" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A38" s="13">
+      <c r="A38" s="9">
         <v>46276</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="11">
         <v>783942599</v>
       </c>
-      <c r="G38" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="14" t="s">
+      <c r="G38" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K38" s="14" t="s">
+      <c r="K38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L38" s="14">
+      <c r="L38" s="10">
         <v>25</v>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="12">
         <v>9000</v>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="12">
         <v>225000</v>
       </c>
-      <c r="O38" s="17" t="str">
+      <c r="O38" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P38" s="18" t="str">
+      <c r="P38" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A39" s="13">
+      <c r="A39" s="9">
         <v>46276</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="11">
         <v>777638400</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J39" s="14" t="s">
+      <c r="H39" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="10">
         <v>2</v>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="12">
         <v>15500</v>
       </c>
-      <c r="N39" s="16">
+      <c r="N39" s="12">
         <v>31000</v>
       </c>
-      <c r="O39" s="17" t="str">
+      <c r="O39" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P39" s="18" t="str">
+      <c r="P39" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A40" s="13">
+      <c r="A40" s="9">
         <v>46276</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="11">
         <v>763578834</v>
       </c>
-      <c r="G40" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="14" t="s">
+      <c r="G40" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K40" s="14" t="s">
+      <c r="K40" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="10">
         <v>25</v>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="12">
         <v>11250</v>
       </c>
-      <c r="N40" s="16">
+      <c r="N40" s="12">
         <v>281250</v>
       </c>
-      <c r="O40" s="17" t="str">
+      <c r="O40" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P40" s="18" t="str">
+      <c r="P40" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A41" s="13">
+      <c r="A41" s="9">
         <v>46276</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="11">
         <v>774333344</v>
       </c>
-      <c r="G41" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="14" t="s">
+      <c r="G41" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K41" s="14" t="s">
+      <c r="K41" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="10">
         <v>5</v>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="12">
         <v>6500</v>
       </c>
-      <c r="N41" s="16">
+      <c r="N41" s="12">
         <v>32500</v>
       </c>
-      <c r="O41" s="17" t="str">
+      <c r="O41" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P41" s="18" t="str">
+      <c r="P41" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A42" s="13">
+      <c r="A42" s="9">
         <v>46276</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="11">
         <v>774216341</v>
       </c>
-      <c r="G42" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="14" t="s">
+      <c r="G42" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K42" s="14" t="s">
+      <c r="K42" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="10">
         <v>25</v>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="12">
         <v>26000</v>
       </c>
-      <c r="N42" s="16">
+      <c r="N42" s="12">
         <v>650000</v>
       </c>
-      <c r="O42" s="17" t="str">
+      <c r="O42" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P42" s="18" t="str">
+      <c r="P42" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A43" s="13">
+      <c r="A43" s="9">
         <v>46276</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="11">
         <v>779236547</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H43" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="14" t="s">
+      <c r="H43" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K43" s="14" t="s">
+      <c r="K43" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="10">
         <v>25</v>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="12">
         <v>6500</v>
       </c>
-      <c r="N43" s="16">
+      <c r="N43" s="12">
         <v>162500</v>
       </c>
-      <c r="O43" s="17" t="str">
+      <c r="O43" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P43" s="18" t="str">
+      <c r="P43" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A44" s="13">
+      <c r="A44" s="9">
         <v>46276</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="11">
         <v>760169386</v>
       </c>
-      <c r="G44" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="14" t="s">
+      <c r="G44" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K44" s="14" t="s">
+      <c r="K44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="10">
         <v>100</v>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="12">
         <v>9000</v>
       </c>
-      <c r="N44" s="16">
+      <c r="N44" s="12">
         <v>900000</v>
       </c>
-      <c r="O44" s="17" t="str">
+      <c r="O44" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P44" s="18" t="str">
+      <c r="P44" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A45" s="13">
+      <c r="A45" s="9">
         <v>46276</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="11">
         <v>777638400</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="14" t="s">
+      <c r="H45" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K45" s="14" t="s">
+      <c r="K45" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="10">
         <v>2</v>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="12">
         <v>15500</v>
       </c>
-      <c r="N45" s="16">
+      <c r="N45" s="12">
         <v>31000</v>
       </c>
-      <c r="O45" s="17" t="str">
+      <c r="O45" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P45" s="18" t="str">
+      <c r="P45" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A46" s="13">
+      <c r="A46" s="9">
         <v>46276</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46" s="11">
         <v>777638400</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H46" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="14" t="s">
+      <c r="H46" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K46" s="14" t="s">
+      <c r="K46" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="L46" s="14">
+      <c r="L46" s="10">
         <v>1</v>
       </c>
-      <c r="M46" s="16">
+      <c r="M46" s="12">
         <v>4500</v>
       </c>
-      <c r="N46" s="16">
+      <c r="N46" s="12">
         <v>4500</v>
       </c>
-      <c r="O46" s="17" t="str">
+      <c r="O46" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P46" s="18" t="str">
+      <c r="P46" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A47" s="13">
+      <c r="A47" s="9">
         <v>46276</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="11">
         <v>775398902</v>
       </c>
-      <c r="G47" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="14" t="s">
+      <c r="G47" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K47" s="14" t="s">
+      <c r="K47" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L47" s="14">
+      <c r="L47" s="10">
         <v>1</v>
       </c>
-      <c r="M47" s="16">
+      <c r="M47" s="12">
         <v>15500</v>
       </c>
-      <c r="N47" s="16">
+      <c r="N47" s="12">
         <v>15500</v>
       </c>
-      <c r="O47" s="17" t="str">
+      <c r="O47" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P47" s="18" t="str">
+      <c r="P47" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A48" s="13">
+      <c r="A48" s="9">
         <v>46276</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="F48" s="15">
+      <c r="F48" s="11">
         <v>775626425</v>
       </c>
-      <c r="G48" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="14" t="s">
+      <c r="G48" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K48" s="14" t="s">
+      <c r="K48" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L48" s="14">
+      <c r="L48" s="10">
         <v>1</v>
       </c>
-      <c r="M48" s="16">
+      <c r="M48" s="12">
         <v>15500</v>
       </c>
-      <c r="N48" s="16">
+      <c r="N48" s="12">
         <v>15500</v>
       </c>
-      <c r="O48" s="17" t="str">
+      <c r="O48" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P48" s="18" t="str">
+      <c r="P48" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A49" s="13">
+      <c r="A49" s="9">
         <v>46276</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="11">
         <v>775541532</v>
       </c>
-      <c r="G49" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14" t="s">
+      <c r="G49" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L49" s="14">
+      <c r="L49" s="10">
         <v>25</v>
       </c>
-      <c r="M49" s="16">
+      <c r="M49" s="12">
         <v>26000</v>
       </c>
-      <c r="N49" s="16">
+      <c r="N49" s="12">
         <v>650000</v>
       </c>
-      <c r="O49" s="17" t="str">
+      <c r="O49" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P49" s="18" t="str">
+      <c r="P49" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A50" s="13">
+      <c r="A50" s="9">
         <v>46274</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F50" s="15">
+      <c r="F50" s="11">
         <v>781728925</v>
       </c>
-      <c r="G50" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" s="14" t="s">
+      <c r="G50" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="I50" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="14" t="s">
+      <c r="I50" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K50" s="14" t="s">
+      <c r="K50" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="L50" s="14">
+      <c r="L50" s="10">
         <v>25</v>
       </c>
-      <c r="M50" s="16">
+      <c r="M50" s="12">
         <v>6500</v>
       </c>
-      <c r="N50" s="16">
+      <c r="N50" s="12">
         <v>162500</v>
       </c>
-      <c r="O50" s="17" t="str">
+      <c r="O50" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P50" s="18" t="str">
+      <c r="P50" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A51" s="13">
+      <c r="A51" s="9">
         <v>46274</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="11">
         <v>785459209</v>
       </c>
-      <c r="G51" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I51" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" s="14" t="s">
+      <c r="G51" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K51" s="14" t="s">
+      <c r="K51" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L51" s="14">
-        <v>15</v>
-      </c>
-      <c r="M51" s="16">
+      <c r="L51" s="10">
+        <v>15</v>
+      </c>
+      <c r="M51" s="12">
         <v>26000</v>
       </c>
-      <c r="N51" s="16">
+      <c r="N51" s="12">
         <v>390000</v>
       </c>
-      <c r="O51" s="17" t="str">
+      <c r="O51" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P51" s="18" t="str">
+      <c r="P51" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A52" s="13">
+      <c r="A52" s="9">
         <v>46274</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F52" s="15">
+      <c r="F52" s="11">
         <v>773366070</v>
       </c>
-      <c r="G52" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="14" t="s">
+      <c r="G52" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K52" s="14" t="s">
+      <c r="K52" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L52" s="14">
+      <c r="L52" s="10">
         <v>10</v>
       </c>
-      <c r="M52" s="16">
+      <c r="M52" s="12">
         <v>28000</v>
       </c>
-      <c r="N52" s="16">
+      <c r="N52" s="12">
         <v>280000</v>
       </c>
-      <c r="O52" s="17" t="str">
+      <c r="O52" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P52" s="18" t="str">
+      <c r="P52" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A53" s="13">
+      <c r="A53" s="9">
         <v>46274</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F53" s="15">
+      <c r="F53" s="11">
         <v>772377240</v>
       </c>
-      <c r="G53" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I53" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="14" t="s">
+      <c r="G53" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K53" s="14" t="s">
+      <c r="K53" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L53" s="14">
+      <c r="L53" s="10">
         <v>25</v>
       </c>
-      <c r="M53" s="16">
+      <c r="M53" s="12">
         <v>19500</v>
       </c>
-      <c r="N53" s="16">
+      <c r="N53" s="12">
         <v>487500</v>
       </c>
-      <c r="O53" s="17" t="str">
+      <c r="O53" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P53" s="18" t="str">
+      <c r="P53" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A54" s="13">
+      <c r="A54" s="9">
         <v>46274</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F54" s="15">
+      <c r="F54" s="11">
         <v>774245132</v>
       </c>
-      <c r="G54" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I54" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14" t="s">
+      <c r="G54" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L54" s="14">
+      <c r="L54" s="10">
         <v>50</v>
       </c>
-      <c r="M54" s="16">
+      <c r="M54" s="12">
         <v>26000</v>
       </c>
-      <c r="N54" s="16">
+      <c r="N54" s="12">
         <v>1300000</v>
       </c>
-      <c r="O54" s="17" t="str">
+      <c r="O54" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P54" s="18" t="str">
+      <c r="P54" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A55" s="13">
+      <c r="A55" s="9">
         <v>46274</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F55" s="15">
+      <c r="F55" s="11">
         <v>784537895</v>
       </c>
-      <c r="G55" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I55" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14" t="s">
+      <c r="G55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L55" s="14">
+      <c r="L55" s="10">
         <v>50</v>
       </c>
-      <c r="M55" s="16">
+      <c r="M55" s="12">
         <v>26000</v>
       </c>
-      <c r="N55" s="16">
+      <c r="N55" s="12">
         <v>1300000</v>
       </c>
-      <c r="O55" s="17" t="str">
+      <c r="O55" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P55" s="18" t="str">
+      <c r="P55" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A56" s="13">
+      <c r="A56" s="9">
         <v>46273</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="F56" s="15">
+      <c r="F56" s="11">
         <v>773531341</v>
       </c>
-      <c r="G56" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I56" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14" t="s">
+      <c r="G56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L56" s="14">
+      <c r="L56" s="10">
         <v>200</v>
       </c>
-      <c r="M56" s="16">
+      <c r="M56" s="12">
         <v>26000</v>
       </c>
-      <c r="N56" s="16">
+      <c r="N56" s="12">
         <v>5200000</v>
       </c>
-      <c r="O56" s="17" t="str">
+      <c r="O56" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P56" s="18" t="str">
+      <c r="P56" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A57" s="13">
+      <c r="A57" s="9">
         <v>46273</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F57" s="15">
+      <c r="F57" s="11">
         <v>775661455</v>
       </c>
-      <c r="G57" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J57" s="14" t="s">
+      <c r="G57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K57" s="14" t="s">
+      <c r="K57" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L57" s="14">
+      <c r="L57" s="10">
         <v>25</v>
       </c>
-      <c r="M57" s="16">
+      <c r="M57" s="12">
         <v>26000</v>
       </c>
-      <c r="N57" s="16">
+      <c r="N57" s="12">
         <v>650000</v>
       </c>
-      <c r="O57" s="17" t="str">
+      <c r="O57" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P57" s="18" t="str">
+      <c r="P57" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A58" s="13">
+      <c r="A58" s="9">
         <v>46273</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F58" s="15">
+      <c r="F58" s="11">
         <v>775661455</v>
       </c>
-      <c r="G58" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I58" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" s="14" t="s">
+      <c r="G58" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K58" s="14" t="s">
+      <c r="K58" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L58" s="14">
+      <c r="L58" s="10">
         <v>25</v>
       </c>
-      <c r="M58" s="16">
+      <c r="M58" s="12">
         <v>19500</v>
       </c>
-      <c r="N58" s="16">
+      <c r="N58" s="12">
         <v>487500</v>
       </c>
-      <c r="O58" s="17" t="str">
+      <c r="O58" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P58" s="18" t="str">
+      <c r="P58" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A59" s="13">
+      <c r="A59" s="9">
         <v>46273</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F59" s="15">
+      <c r="F59" s="11">
         <v>783758073</v>
       </c>
-      <c r="G59" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="14" t="s">
+      <c r="G59" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K59" s="14" t="s">
+      <c r="K59" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L59" s="14">
+      <c r="L59" s="10">
         <v>25</v>
       </c>
-      <c r="M59" s="16">
+      <c r="M59" s="12">
         <v>28000</v>
       </c>
-      <c r="N59" s="16">
+      <c r="N59" s="12">
         <v>700000</v>
       </c>
-      <c r="O59" s="17" t="str">
+      <c r="O59" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S37</v>
       </c>
-      <c r="P59" s="18" t="str">
+      <c r="P59" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A60" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60" s="15">
+        <v>776561455</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L60" s="16">
+        <v>25</v>
+      </c>
+      <c r="M60" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N60" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O60" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P60" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A61" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="15">
+        <v>776561455</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="16"/>
+      <c r="K61" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="16">
+        <v>1</v>
+      </c>
+      <c r="M61" s="17">
+        <v>11500</v>
+      </c>
+      <c r="N61" s="17">
+        <v>11500</v>
+      </c>
+      <c r="O61" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P61" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A62" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F62" s="15">
+        <v>776561455</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L62" s="16">
+        <v>1</v>
+      </c>
+      <c r="M62" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N62" s="17">
+        <v>15500</v>
+      </c>
+      <c r="O62" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P62" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A63" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F63" s="15">
+        <v>776561455</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L63" s="14">
+        <v>10</v>
+      </c>
+      <c r="M63" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N63" s="18">
+        <v>65000</v>
+      </c>
+      <c r="O63" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P63" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A64" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F64" s="15">
+        <v>764883712</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L64" s="14">
+        <v>40</v>
+      </c>
+      <c r="M64" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N64" s="18">
+        <v>360000</v>
+      </c>
+      <c r="O64" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P64" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A65" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F65" s="15">
+        <v>779236547</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" s="14">
+        <v>25</v>
+      </c>
+      <c r="M65" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N65" s="18">
+        <v>650000</v>
+      </c>
+      <c r="O65" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P65" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A66" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F66" s="15">
+        <v>779236547</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I66" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L66" s="14">
+        <v>25</v>
+      </c>
+      <c r="M66" s="18">
+        <v>11250</v>
+      </c>
+      <c r="N66" s="18">
+        <v>281250</v>
+      </c>
+      <c r="O66" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P66" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A67" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F67" s="15">
+        <v>776149093</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="L67" s="14">
+        <v>60</v>
+      </c>
+      <c r="M67" s="18">
+        <v>4000</v>
+      </c>
+      <c r="N67" s="18">
+        <v>240000</v>
+      </c>
+      <c r="O67" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P67" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A68" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F68" s="15">
+        <v>770158721</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="L68" s="14">
+        <v>25</v>
+      </c>
+      <c r="M68" s="18">
+        <v>15500</v>
+      </c>
+      <c r="N68" s="18">
+        <v>387500</v>
+      </c>
+      <c r="O68" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P68" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A69" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F69" s="15">
+        <v>770158721</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L69" s="14">
+        <v>25</v>
+      </c>
+      <c r="M69" s="18">
+        <v>15500</v>
+      </c>
+      <c r="N69" s="18">
+        <v>387500</v>
+      </c>
+      <c r="O69" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P69" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A70" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F70" s="15">
+        <v>770158721</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L70" s="14">
+        <v>30</v>
+      </c>
+      <c r="M70" s="18">
+        <v>11500</v>
+      </c>
+      <c r="N70" s="18">
+        <v>345000</v>
+      </c>
+      <c r="O70" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P70" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A71" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F71" s="15">
+        <v>774277399</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L71" s="14">
+        <v>20</v>
+      </c>
+      <c r="M71" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N71" s="18">
+        <v>180000</v>
+      </c>
+      <c r="O71" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P71" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A72" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F72" s="15">
+        <v>773546192</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L72" s="14">
+        <v>10</v>
+      </c>
+      <c r="M72" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N72" s="18">
+        <v>90000</v>
+      </c>
+      <c r="O72" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P72" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A73" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F73" s="15">
+        <v>778657940</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" s="14">
+        <v>50</v>
+      </c>
+      <c r="M73" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N73" s="18">
+        <v>450000</v>
+      </c>
+      <c r="O73" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P73" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A74" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" s="15">
+        <v>767267003</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" s="14">
+        <v>25</v>
+      </c>
+      <c r="M74" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N74" s="18">
+        <v>650000</v>
+      </c>
+      <c r="O74" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P74" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A75" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E75" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F75" s="15">
+        <v>767379110</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L75" s="14">
+        <v>25</v>
+      </c>
+      <c r="M75" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N75" s="18">
+        <v>225000</v>
+      </c>
+      <c r="O75" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P75" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A76" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F76" s="15">
+        <v>767379110</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L76" s="14">
+        <v>7</v>
+      </c>
+      <c r="M76" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N76" s="18">
+        <v>45500</v>
+      </c>
+      <c r="O76" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P76" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A77" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F77" s="15">
+        <v>767379110</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L77" s="14">
+        <v>2</v>
+      </c>
+      <c r="M77" s="18">
+        <v>15500</v>
+      </c>
+      <c r="N77" s="18">
+        <v>31000</v>
+      </c>
+      <c r="O77" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P77" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A78" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F78" s="15">
+        <v>775582583</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="L78" s="14">
+        <v>25</v>
+      </c>
+      <c r="M78" s="18">
+        <v>28000</v>
+      </c>
+      <c r="N78" s="18">
+        <v>700000</v>
+      </c>
+      <c r="O78" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P78" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A79" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F79" s="15">
+        <v>786323232</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L79" s="14">
+        <v>25</v>
+      </c>
+      <c r="M79" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N79" s="18">
+        <v>225000</v>
+      </c>
+      <c r="O79" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P79" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A80" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F80" s="15">
+        <v>778195274</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L80" s="14">
+        <v>100</v>
+      </c>
+      <c r="M80" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N80" s="18">
+        <v>2600000</v>
+      </c>
+      <c r="O80" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P80" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A81" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E81" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F81" s="15">
+        <v>784208258</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K81" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L81" s="14">
+        <v>5</v>
+      </c>
+      <c r="M81" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N81" s="18">
+        <v>45000</v>
+      </c>
+      <c r="O81" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P81" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A82" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F82" s="15">
+        <v>777802399</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L82" s="14">
+        <v>1</v>
+      </c>
+      <c r="M82" s="18">
+        <v>12500</v>
+      </c>
+      <c r="N82" s="18">
+        <v>12500</v>
+      </c>
+      <c r="O82" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P82" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A83" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F83" s="15">
+        <v>777802399</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="L83" s="14">
+        <v>1</v>
+      </c>
+      <c r="M83" s="18">
+        <v>15500</v>
+      </c>
+      <c r="N83" s="18">
+        <v>15500</v>
+      </c>
+      <c r="O83" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P83" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A84" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F84" s="15">
+        <v>777802399</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L84" s="14">
+        <v>1</v>
+      </c>
+      <c r="M84" s="18">
+        <v>11250</v>
+      </c>
+      <c r="N84" s="18">
+        <v>11250</v>
+      </c>
+      <c r="O84" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P84" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A85" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F85" s="15">
+        <v>778276533</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L85" s="14">
+        <v>2</v>
+      </c>
+      <c r="M85" s="18">
+        <v>15500</v>
+      </c>
+      <c r="N85" s="18">
+        <v>31000</v>
+      </c>
+      <c r="O85" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P85" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A86" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F86" s="15">
+        <v>778276533</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L86" s="14">
+        <v>2</v>
+      </c>
+      <c r="M86" s="18">
+        <v>12500</v>
+      </c>
+      <c r="N86" s="18">
+        <v>25000</v>
+      </c>
+      <c r="O86" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P86" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A87" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E87" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F87" s="15">
+        <v>778276533</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="K87" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L87" s="14">
+        <v>1</v>
+      </c>
+      <c r="M87" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N87" s="18">
+        <v>6500</v>
+      </c>
+      <c r="O87" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P87" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A88" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F88" s="15">
+        <v>778276533</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I88" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="K88" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L88" s="14">
+        <v>2</v>
+      </c>
+      <c r="M88" s="18">
+        <v>11250</v>
+      </c>
+      <c r="N88" s="18">
+        <v>22500</v>
+      </c>
+      <c r="O88" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P88" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A89" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E89" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F89" s="15">
+        <v>773248259</v>
+      </c>
+      <c r="G89" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H89" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K89" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L89" s="14">
+        <v>1</v>
+      </c>
+      <c r="M89" s="18">
+        <v>19500</v>
+      </c>
+      <c r="N89" s="18">
+        <v>19500</v>
+      </c>
+      <c r="O89" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P89" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A90" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F90" s="15">
+        <v>773248259</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K90" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L90" s="14">
+        <v>2</v>
+      </c>
+      <c r="M90" s="18">
+        <v>19500</v>
+      </c>
+      <c r="N90" s="18">
+        <v>39000</v>
+      </c>
+      <c r="O90" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P90" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A91" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F91" s="15">
+        <v>773248259</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I91" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K91" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L91" s="14">
+        <v>5</v>
+      </c>
+      <c r="M91" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N91" s="18">
+        <v>45000</v>
+      </c>
+      <c r="O91" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P91" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A92" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F92" s="15">
+        <v>777802399</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K92" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L92" s="14">
+        <v>1</v>
+      </c>
+      <c r="M92" s="18">
+        <v>15500</v>
+      </c>
+      <c r="N92" s="18">
+        <v>15500</v>
+      </c>
+      <c r="O92" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P92" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A93" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E93" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F93" s="15">
+        <v>767379110</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K93" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L93" s="14">
+        <v>2</v>
+      </c>
+      <c r="M93" s="18">
+        <v>11250</v>
+      </c>
+      <c r="N93" s="18">
+        <v>22500</v>
+      </c>
+      <c r="O93" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P93" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A94" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F94" s="15">
+        <v>773066194</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K94" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L94" s="14">
+        <v>25</v>
+      </c>
+      <c r="M94" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N94" s="18">
+        <v>650000</v>
+      </c>
+      <c r="O94" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P94" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A95" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E95" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F95" s="15">
+        <v>774289051</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K95" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L95" s="14">
+        <v>25</v>
+      </c>
+      <c r="M95" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N95" s="18">
+        <v>650000</v>
+      </c>
+      <c r="O95" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P95" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A96" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F96" s="15">
+        <v>782442821</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="K96" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L96" s="14">
+        <v>5</v>
+      </c>
+      <c r="M96" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N96" s="18">
+        <v>45000</v>
+      </c>
+      <c r="O96" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P96" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A97" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="E97" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="F97" s="15">
+        <v>775276149</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K97" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L97" s="14">
+        <v>5</v>
+      </c>
+      <c r="M97" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N97" s="18">
+        <v>32500</v>
+      </c>
+      <c r="O97" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P97" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A98" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="F98" s="15">
+        <v>775894237</v>
+      </c>
+      <c r="G98" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K98" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L98" s="14">
+        <v>30</v>
+      </c>
+      <c r="M98" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N98" s="18">
+        <v>270000</v>
+      </c>
+      <c r="O98" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P98" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A99" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F99" s="15">
+        <v>776175166</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="K99" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L99" s="14">
+        <v>100</v>
+      </c>
+      <c r="M99" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N99" s="18">
+        <v>2600000</v>
+      </c>
+      <c r="O99" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P99" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A100" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F100" s="15">
+        <v>776622000</v>
+      </c>
+      <c r="G100" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="K100" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L100" s="14">
+        <v>25</v>
+      </c>
+      <c r="M100" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N100" s="18">
+        <v>162500</v>
+      </c>
+      <c r="O100" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P100" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A101" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F101" s="15">
+        <v>775039973</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="K101" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L101" s="14">
+        <v>25</v>
+      </c>
+      <c r="M101" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N101" s="18">
+        <v>650000</v>
+      </c>
+      <c r="O101" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P101" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A102" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B102" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F102" s="15">
+        <v>776328716</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L102" s="14">
+        <v>25</v>
+      </c>
+      <c r="M102" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N102" s="18">
+        <v>650000</v>
+      </c>
+      <c r="O102" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P102" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A103" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B103" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E103" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="F103" s="15">
+        <v>774927422</v>
+      </c>
+      <c r="G103" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K103" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L103" s="14">
+        <v>25</v>
+      </c>
+      <c r="M103" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N103" s="18">
+        <v>650000</v>
+      </c>
+      <c r="O103" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P103" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A104" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F104" s="15">
+        <v>773122246</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="K104" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L104" s="14">
+        <v>25</v>
+      </c>
+      <c r="M104" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N104" s="18">
+        <v>225000</v>
+      </c>
+      <c r="O104" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S38</v>
+      </c>
+      <c r="P104" s="20" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44372A2E-0F04-4481-80EA-9F33FD7CA3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93BF5CC-7B69-41D4-95DE-6A6345DB53D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="191">
   <si>
     <t>Date</t>
   </si>
@@ -564,6 +564,48 @@
   </si>
   <si>
     <t>Serigne Fallou GAYE</t>
+  </si>
+  <si>
+    <t>Abdou Wagué</t>
+  </si>
+  <si>
+    <t>Chocolat transparent 400gx12pcs</t>
+  </si>
+  <si>
+    <t>Kayar</t>
+  </si>
+  <si>
+    <t>Babacar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À commander </t>
+  </si>
+  <si>
+    <t>Mame Serigne</t>
+  </si>
+  <si>
+    <t>Stapro.com SARL n1</t>
+  </si>
+  <si>
+    <t>Il demande de diminuer le prix du lait concentré</t>
+  </si>
+  <si>
+    <t>Je vais essayer avec</t>
+  </si>
+  <si>
+    <t>Issa  Diallo</t>
+  </si>
+  <si>
+    <t>Zac Mbao</t>
+  </si>
+  <si>
+    <t>Tierno</t>
+  </si>
+  <si>
+    <t>Bayakh</t>
+  </si>
+  <si>
+    <t>Bathie</t>
   </si>
 </sst>
 </file>
@@ -670,6 +712,12 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -677,12 +725,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -997,8 +1039,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P104" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P104" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P118" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P118" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1311,7 +1353,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -4384,2325 +4426,3053 @@
       </c>
     </row>
     <row r="60" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A60" s="13">
+      <c r="A60" s="9">
         <v>46284</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F60" s="15">
+      <c r="F60" s="11">
         <v>776561455</v>
       </c>
-      <c r="G60" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16" t="s">
+      <c r="G60" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="L60" s="16">
+      <c r="L60" s="13">
         <v>25</v>
       </c>
-      <c r="M60" s="17">
+      <c r="M60" s="14">
         <v>9000</v>
       </c>
-      <c r="N60" s="17">
+      <c r="N60" s="14">
         <v>225000</v>
       </c>
-      <c r="O60" s="19" t="str">
+      <c r="O60" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P60" s="20" t="str">
+      <c r="P60" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A61" s="13">
+      <c r="A61" s="9">
         <v>46284</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F61" s="15">
+      <c r="F61" s="11">
         <v>776561455</v>
       </c>
-      <c r="G61" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I61" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="16"/>
-      <c r="K61" s="16" t="s">
+      <c r="G61" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="L61" s="16">
+      <c r="L61" s="13">
         <v>1</v>
       </c>
-      <c r="M61" s="17">
+      <c r="M61" s="14">
         <v>11500</v>
       </c>
-      <c r="N61" s="17">
+      <c r="N61" s="14">
         <v>11500</v>
       </c>
-      <c r="O61" s="19" t="str">
+      <c r="O61" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P61" s="20" t="str">
+      <c r="P61" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A62" s="13">
+      <c r="A62" s="9">
         <v>46284</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F62" s="15">
+      <c r="F62" s="11">
         <v>776561455</v>
       </c>
-      <c r="G62" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J62" s="16"/>
-      <c r="K62" s="16" t="s">
+      <c r="G62" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="L62" s="16">
+      <c r="L62" s="13">
         <v>1</v>
       </c>
-      <c r="M62" s="17">
+      <c r="M62" s="14">
         <v>15500</v>
       </c>
-      <c r="N62" s="17">
+      <c r="N62" s="14">
         <v>15500</v>
       </c>
-      <c r="O62" s="19" t="str">
+      <c r="O62" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P62" s="20" t="str">
+      <c r="P62" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A63" s="13">
+      <c r="A63" s="9">
         <v>46284</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="F63" s="15">
+      <c r="F63" s="11">
         <v>776561455</v>
       </c>
-      <c r="G63" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I63" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J63" s="14" t="s">
+      <c r="G63" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K63" s="14" t="s">
+      <c r="K63" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L63" s="14">
+      <c r="L63" s="10">
         <v>10</v>
       </c>
-      <c r="M63" s="18">
+      <c r="M63" s="12">
         <v>6500</v>
       </c>
-      <c r="N63" s="18">
+      <c r="N63" s="12">
         <v>65000</v>
       </c>
-      <c r="O63" s="19" t="str">
+      <c r="O63" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P63" s="20" t="str">
+      <c r="P63" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A64" s="13">
+      <c r="A64" s="9">
         <v>46283</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="F64" s="15">
+      <c r="F64" s="11">
         <v>764883712</v>
       </c>
-      <c r="G64" s="14" t="s">
+      <c r="G64" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="H64" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I64" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="14" t="s">
+      <c r="H64" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K64" s="14" t="s">
+      <c r="K64" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L64" s="14">
+      <c r="L64" s="10">
         <v>40</v>
       </c>
-      <c r="M64" s="18">
+      <c r="M64" s="12">
         <v>9000</v>
       </c>
-      <c r="N64" s="18">
+      <c r="N64" s="12">
         <v>360000</v>
       </c>
-      <c r="O64" s="19" t="str">
+      <c r="O64" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P64" s="20" t="str">
+      <c r="P64" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A65" s="13">
+      <c r="A65" s="9">
         <v>46283</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E65" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F65" s="15">
+      <c r="F65" s="11">
         <v>779236547</v>
       </c>
-      <c r="G65" s="14" t="s">
+      <c r="G65" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H65" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I65" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="14" t="s">
+      <c r="H65" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K65" s="14" t="s">
+      <c r="K65" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L65" s="14">
+      <c r="L65" s="10">
         <v>25</v>
       </c>
-      <c r="M65" s="18">
+      <c r="M65" s="12">
         <v>26000</v>
       </c>
-      <c r="N65" s="18">
+      <c r="N65" s="12">
         <v>650000</v>
       </c>
-      <c r="O65" s="19" t="str">
+      <c r="O65" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P65" s="20" t="str">
+      <c r="P65" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A66" s="13">
+      <c r="A66" s="9">
         <v>46283</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F66" s="15">
+      <c r="F66" s="11">
         <v>779236547</v>
       </c>
-      <c r="G66" s="14" t="s">
+      <c r="G66" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H66" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I66" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" s="14" t="s">
+      <c r="H66" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K66" s="14" t="s">
+      <c r="K66" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L66" s="14">
+      <c r="L66" s="10">
         <v>25</v>
       </c>
-      <c r="M66" s="18">
+      <c r="M66" s="12">
         <v>11250</v>
       </c>
-      <c r="N66" s="18">
+      <c r="N66" s="12">
         <v>281250</v>
       </c>
-      <c r="O66" s="19" t="str">
+      <c r="O66" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P66" s="20" t="str">
+      <c r="P66" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A67" s="13">
+      <c r="A67" s="9">
         <v>46282</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="14" t="s">
+      <c r="D67" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E67" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F67" s="15">
+      <c r="F67" s="11">
         <v>776149093</v>
       </c>
-      <c r="G67" s="14" t="s">
+      <c r="G67" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H67" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I67" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14" t="s">
+      <c r="H67" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="L67" s="14">
+      <c r="L67" s="10">
         <v>60</v>
       </c>
-      <c r="M67" s="18">
+      <c r="M67" s="12">
         <v>4000</v>
       </c>
-      <c r="N67" s="18">
+      <c r="N67" s="12">
         <v>240000</v>
       </c>
-      <c r="O67" s="19" t="str">
+      <c r="O67" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P67" s="20" t="str">
+      <c r="P67" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A68" s="13">
+      <c r="A68" s="9">
         <v>46282</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F68" s="15">
+      <c r="F68" s="11">
         <v>770158721</v>
       </c>
-      <c r="G68" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I68" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" s="14" t="s">
+      <c r="G68" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K68" s="14" t="s">
+      <c r="K68" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="L68" s="14">
+      <c r="L68" s="10">
         <v>25</v>
       </c>
-      <c r="M68" s="18">
+      <c r="M68" s="12">
         <v>15500</v>
       </c>
-      <c r="N68" s="18">
+      <c r="N68" s="12">
         <v>387500</v>
       </c>
-      <c r="O68" s="19" t="str">
+      <c r="O68" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P68" s="20" t="str">
+      <c r="P68" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A69" s="13">
+      <c r="A69" s="9">
         <v>46282</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F69" s="15">
+      <c r="F69" s="11">
         <v>770158721</v>
       </c>
-      <c r="G69" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I69" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="14" t="s">
+      <c r="G69" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K69" s="14" t="s">
+      <c r="K69" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L69" s="14">
+      <c r="L69" s="10">
         <v>25</v>
       </c>
-      <c r="M69" s="18">
+      <c r="M69" s="12">
         <v>15500</v>
       </c>
-      <c r="N69" s="18">
+      <c r="N69" s="12">
         <v>387500</v>
       </c>
-      <c r="O69" s="19" t="str">
+      <c r="O69" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P69" s="20" t="str">
+      <c r="P69" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A70" s="13">
+      <c r="A70" s="9">
         <v>46282</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F70" s="15">
+      <c r="F70" s="11">
         <v>770158721</v>
       </c>
-      <c r="G70" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" s="14" t="s">
+      <c r="G70" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K70" s="14" t="s">
+      <c r="K70" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L70" s="14">
+      <c r="L70" s="10">
         <v>30</v>
       </c>
-      <c r="M70" s="18">
+      <c r="M70" s="12">
         <v>11500</v>
       </c>
-      <c r="N70" s="18">
+      <c r="N70" s="12">
         <v>345000</v>
       </c>
-      <c r="O70" s="19" t="str">
+      <c r="O70" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P70" s="20" t="str">
+      <c r="P70" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A71" s="13">
+      <c r="A71" s="9">
         <v>46281</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="F71" s="15">
+      <c r="F71" s="11">
         <v>774277399</v>
       </c>
-      <c r="G71" s="14" t="s">
+      <c r="G71" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H71" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14" t="s">
+      <c r="H71" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L71" s="14">
+      <c r="L71" s="10">
         <v>20</v>
       </c>
-      <c r="M71" s="18">
+      <c r="M71" s="12">
         <v>9000</v>
       </c>
-      <c r="N71" s="18">
+      <c r="N71" s="12">
         <v>180000</v>
       </c>
-      <c r="O71" s="19" t="str">
+      <c r="O71" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P71" s="20" t="str">
+      <c r="P71" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A72" s="13">
+      <c r="A72" s="9">
         <v>46281</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E72" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F72" s="15">
+      <c r="F72" s="11">
         <v>773546192</v>
       </c>
-      <c r="G72" s="14" t="s">
+      <c r="G72" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H72" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I72" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14" t="s">
+      <c r="H72" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L72" s="14">
+      <c r="L72" s="10">
         <v>10</v>
       </c>
-      <c r="M72" s="18">
+      <c r="M72" s="12">
         <v>9000</v>
       </c>
-      <c r="N72" s="18">
+      <c r="N72" s="12">
         <v>90000</v>
       </c>
-      <c r="O72" s="19" t="str">
+      <c r="O72" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P72" s="20" t="str">
+      <c r="P72" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A73" s="13">
+      <c r="A73" s="9">
         <v>46281</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F73" s="15">
+      <c r="F73" s="11">
         <v>778657940</v>
       </c>
-      <c r="G73" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="14" t="s">
+      <c r="G73" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K73" s="14" t="s">
+      <c r="K73" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L73" s="14">
+      <c r="L73" s="10">
         <v>50</v>
       </c>
-      <c r="M73" s="18">
+      <c r="M73" s="12">
         <v>9000</v>
       </c>
-      <c r="N73" s="18">
+      <c r="N73" s="12">
         <v>450000</v>
       </c>
-      <c r="O73" s="19" t="str">
+      <c r="O73" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P73" s="20" t="str">
+      <c r="P73" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A74" s="13">
+      <c r="A74" s="9">
         <v>46281</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D74" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="E74" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="F74" s="15">
+      <c r="F74" s="11">
         <v>767267003</v>
       </c>
-      <c r="G74" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" s="14" t="s">
+      <c r="G74" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K74" s="14" t="s">
+      <c r="K74" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L74" s="14">
+      <c r="L74" s="10">
         <v>25</v>
       </c>
-      <c r="M74" s="18">
+      <c r="M74" s="12">
         <v>26000</v>
       </c>
-      <c r="N74" s="18">
+      <c r="N74" s="12">
         <v>650000</v>
       </c>
-      <c r="O74" s="19" t="str">
+      <c r="O74" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P74" s="20" t="str">
+      <c r="P74" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A75" s="13">
+      <c r="A75" s="9">
         <v>46280</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F75" s="15">
+      <c r="F75" s="11">
         <v>767379110</v>
       </c>
-      <c r="G75" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J75" s="14" t="s">
+      <c r="G75" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K75" s="14" t="s">
+      <c r="K75" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L75" s="14">
+      <c r="L75" s="10">
         <v>25</v>
       </c>
-      <c r="M75" s="18">
+      <c r="M75" s="12">
         <v>9000</v>
       </c>
-      <c r="N75" s="18">
+      <c r="N75" s="12">
         <v>225000</v>
       </c>
-      <c r="O75" s="19" t="str">
+      <c r="O75" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P75" s="20" t="str">
+      <c r="P75" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A76" s="13">
+      <c r="A76" s="9">
         <v>46280</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E76" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F76" s="15">
+      <c r="F76" s="11">
         <v>767379110</v>
       </c>
-      <c r="G76" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J76" s="14" t="s">
+      <c r="G76" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K76" s="14" t="s">
+      <c r="K76" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L76" s="14">
+      <c r="L76" s="10">
         <v>7</v>
       </c>
-      <c r="M76" s="18">
+      <c r="M76" s="12">
         <v>6500</v>
       </c>
-      <c r="N76" s="18">
+      <c r="N76" s="12">
         <v>45500</v>
       </c>
-      <c r="O76" s="19" t="str">
+      <c r="O76" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P76" s="20" t="str">
+      <c r="P76" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A77" s="13">
+      <c r="A77" s="9">
         <v>46280</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F77" s="15">
+      <c r="F77" s="11">
         <v>767379110</v>
       </c>
-      <c r="G77" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" s="14" t="s">
+      <c r="G77" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K77" s="14" t="s">
+      <c r="K77" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L77" s="14">
+      <c r="L77" s="10">
         <v>2</v>
       </c>
-      <c r="M77" s="18">
+      <c r="M77" s="12">
         <v>15500</v>
       </c>
-      <c r="N77" s="18">
+      <c r="N77" s="12">
         <v>31000</v>
       </c>
-      <c r="O77" s="19" t="str">
+      <c r="O77" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P77" s="20" t="str">
+      <c r="P77" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A78" s="13">
+      <c r="A78" s="9">
         <v>46280</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D78" s="14" t="s">
+      <c r="D78" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F78" s="15">
+      <c r="F78" s="11">
         <v>775582583</v>
       </c>
-      <c r="G78" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J78" s="14"/>
-      <c r="K78" s="14" t="s">
+      <c r="G78" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" s="10"/>
+      <c r="K78" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="L78" s="14">
+      <c r="L78" s="10">
         <v>25</v>
       </c>
-      <c r="M78" s="18">
+      <c r="M78" s="12">
         <v>28000</v>
       </c>
-      <c r="N78" s="18">
+      <c r="N78" s="12">
         <v>700000</v>
       </c>
-      <c r="O78" s="19" t="str">
+      <c r="O78" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P78" s="20" t="str">
+      <c r="P78" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A79" s="13">
+      <c r="A79" s="9">
         <v>46280</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="14" t="s">
+      <c r="D79" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F79" s="15">
+      <c r="F79" s="11">
         <v>786323232</v>
       </c>
-      <c r="G79" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14" t="s">
+      <c r="G79" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="10"/>
+      <c r="K79" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L79" s="14">
+      <c r="L79" s="10">
         <v>25</v>
       </c>
-      <c r="M79" s="18">
+      <c r="M79" s="12">
         <v>9000</v>
       </c>
-      <c r="N79" s="18">
+      <c r="N79" s="12">
         <v>225000</v>
       </c>
-      <c r="O79" s="19" t="str">
+      <c r="O79" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P79" s="20" t="str">
+      <c r="P79" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A80" s="13">
+      <c r="A80" s="9">
         <v>46279</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F80" s="15">
+      <c r="F80" s="11">
         <v>778195274</v>
       </c>
-      <c r="G80" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I80" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" s="14" t="s">
+      <c r="G80" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K80" s="14" t="s">
+      <c r="K80" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L80" s="14">
+      <c r="L80" s="10">
         <v>100</v>
       </c>
-      <c r="M80" s="18">
+      <c r="M80" s="12">
         <v>26000</v>
       </c>
-      <c r="N80" s="18">
+      <c r="N80" s="12">
         <v>2600000</v>
       </c>
-      <c r="O80" s="19" t="str">
+      <c r="O80" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P80" s="20" t="str">
+      <c r="P80" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A81" s="13">
+      <c r="A81" s="9">
         <v>46283</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D81" s="14" t="s">
+      <c r="D81" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="E81" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F81" s="15">
+      <c r="F81" s="11">
         <v>784208258</v>
       </c>
-      <c r="G81" s="14" t="s">
+      <c r="G81" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H81" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I81" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J81" s="14" t="s">
+      <c r="H81" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K81" s="14" t="s">
+      <c r="K81" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L81" s="14">
+      <c r="L81" s="10">
         <v>5</v>
       </c>
-      <c r="M81" s="18">
+      <c r="M81" s="12">
         <v>9000</v>
       </c>
-      <c r="N81" s="18">
+      <c r="N81" s="12">
         <v>45000</v>
       </c>
-      <c r="O81" s="19" t="str">
+      <c r="O81" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P81" s="20" t="str">
+      <c r="P81" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A82" s="13">
+      <c r="A82" s="9">
         <v>46283</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="14" t="s">
+      <c r="D82" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E82" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F82" s="15">
+      <c r="F82" s="11">
         <v>777802399</v>
       </c>
-      <c r="G82" s="14" t="s">
+      <c r="G82" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H82" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I82" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J82" s="14" t="s">
+      <c r="H82" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K82" s="14" t="s">
+      <c r="K82" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="L82" s="14">
+      <c r="L82" s="10">
         <v>1</v>
       </c>
-      <c r="M82" s="18">
+      <c r="M82" s="12">
         <v>12500</v>
       </c>
-      <c r="N82" s="18">
+      <c r="N82" s="12">
         <v>12500</v>
       </c>
-      <c r="O82" s="19" t="str">
+      <c r="O82" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P82" s="20" t="str">
+      <c r="P82" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A83" s="13">
+      <c r="A83" s="9">
         <v>46283</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D83" s="14" t="s">
+      <c r="D83" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E83" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F83" s="15">
+      <c r="F83" s="11">
         <v>777802399</v>
       </c>
-      <c r="G83" s="14" t="s">
+      <c r="G83" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H83" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I83" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="14" t="s">
+      <c r="H83" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K83" s="14" t="s">
+      <c r="K83" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="L83" s="14">
+      <c r="L83" s="10">
         <v>1</v>
       </c>
-      <c r="M83" s="18">
+      <c r="M83" s="12">
         <v>15500</v>
       </c>
-      <c r="N83" s="18">
+      <c r="N83" s="12">
         <v>15500</v>
       </c>
-      <c r="O83" s="19" t="str">
+      <c r="O83" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P83" s="20" t="str">
+      <c r="P83" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A84" s="13">
+      <c r="A84" s="9">
         <v>46283</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D84" s="14" t="s">
+      <c r="D84" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E84" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F84" s="15">
+      <c r="F84" s="11">
         <v>777802399</v>
       </c>
-      <c r="G84" s="14" t="s">
+      <c r="G84" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H84" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I84" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J84" s="14" t="s">
+      <c r="H84" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K84" s="14" t="s">
+      <c r="K84" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L84" s="14">
+      <c r="L84" s="10">
         <v>1</v>
       </c>
-      <c r="M84" s="18">
+      <c r="M84" s="12">
         <v>11250</v>
       </c>
-      <c r="N84" s="18">
+      <c r="N84" s="12">
         <v>11250</v>
       </c>
-      <c r="O84" s="19" t="str">
+      <c r="O84" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P84" s="20" t="str">
+      <c r="P84" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A85" s="13">
+      <c r="A85" s="9">
         <v>46283</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D85" s="14" t="s">
+      <c r="D85" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E85" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F85" s="15">
+      <c r="F85" s="11">
         <v>778276533</v>
       </c>
-      <c r="G85" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H85" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I85" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" s="14" t="s">
+      <c r="G85" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K85" s="14" t="s">
+      <c r="K85" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L85" s="14">
+      <c r="L85" s="10">
         <v>2</v>
       </c>
-      <c r="M85" s="18">
+      <c r="M85" s="12">
         <v>15500</v>
       </c>
-      <c r="N85" s="18">
+      <c r="N85" s="12">
         <v>31000</v>
       </c>
-      <c r="O85" s="19" t="str">
+      <c r="O85" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P85" s="20" t="str">
+      <c r="P85" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A86" s="13">
+      <c r="A86" s="9">
         <v>46283</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D86" s="14" t="s">
+      <c r="D86" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E86" s="14" t="s">
+      <c r="E86" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F86" s="15">
+      <c r="F86" s="11">
         <v>778276533</v>
       </c>
-      <c r="G86" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I86" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J86" s="14" t="s">
+      <c r="G86" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K86" s="14" t="s">
+      <c r="K86" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="L86" s="14">
+      <c r="L86" s="10">
         <v>2</v>
       </c>
-      <c r="M86" s="18">
+      <c r="M86" s="12">
         <v>12500</v>
       </c>
-      <c r="N86" s="18">
+      <c r="N86" s="12">
         <v>25000</v>
       </c>
-      <c r="O86" s="19" t="str">
+      <c r="O86" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P86" s="20" t="str">
+      <c r="P86" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A87" s="13">
+      <c r="A87" s="9">
         <v>46283</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D87" s="14" t="s">
+      <c r="D87" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E87" s="14" t="s">
+      <c r="E87" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F87" s="15">
+      <c r="F87" s="11">
         <v>778276533</v>
       </c>
-      <c r="G87" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I87" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J87" s="14" t="s">
+      <c r="G87" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K87" s="14" t="s">
+      <c r="K87" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L87" s="14">
+      <c r="L87" s="10">
         <v>1</v>
       </c>
-      <c r="M87" s="18">
+      <c r="M87" s="12">
         <v>6500</v>
       </c>
-      <c r="N87" s="18">
+      <c r="N87" s="12">
         <v>6500</v>
       </c>
-      <c r="O87" s="19" t="str">
+      <c r="O87" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P87" s="20" t="str">
+      <c r="P87" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A88" s="13">
+      <c r="A88" s="9">
         <v>46283</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D88" s="14" t="s">
+      <c r="D88" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="E88" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F88" s="15">
+      <c r="F88" s="11">
         <v>778276533</v>
       </c>
-      <c r="G88" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I88" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" s="14" t="s">
+      <c r="G88" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="K88" s="14" t="s">
+      <c r="K88" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L88" s="14">
+      <c r="L88" s="10">
         <v>2</v>
       </c>
-      <c r="M88" s="18">
+      <c r="M88" s="12">
         <v>11250</v>
       </c>
-      <c r="N88" s="18">
+      <c r="N88" s="12">
         <v>22500</v>
       </c>
-      <c r="O88" s="19" t="str">
+      <c r="O88" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P88" s="20" t="str">
+      <c r="P88" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A89" s="13">
+      <c r="A89" s="9">
         <v>46283</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C89" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="14" t="s">
+      <c r="D89" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E89" s="14" t="s">
+      <c r="E89" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F89" s="15">
+      <c r="F89" s="11">
         <v>773248259</v>
       </c>
-      <c r="G89" s="14" t="s">
+      <c r="G89" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="H89" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I89" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J89" s="14" t="s">
+      <c r="H89" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K89" s="14" t="s">
+      <c r="K89" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L89" s="14">
+      <c r="L89" s="10">
         <v>1</v>
       </c>
-      <c r="M89" s="18">
+      <c r="M89" s="12">
         <v>19500</v>
       </c>
-      <c r="N89" s="18">
+      <c r="N89" s="12">
         <v>19500</v>
       </c>
-      <c r="O89" s="19" t="str">
+      <c r="O89" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P89" s="20" t="str">
+      <c r="P89" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A90" s="13">
+      <c r="A90" s="9">
         <v>46283</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D90" s="14" t="s">
+      <c r="D90" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E90" s="14" t="s">
+      <c r="E90" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F90" s="15">
+      <c r="F90" s="11">
         <v>773248259</v>
       </c>
-      <c r="G90" s="14" t="s">
+      <c r="G90" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="H90" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I90" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J90" s="14" t="s">
+      <c r="H90" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K90" s="14" t="s">
+      <c r="K90" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L90" s="14">
+      <c r="L90" s="10">
         <v>2</v>
       </c>
-      <c r="M90" s="18">
+      <c r="M90" s="12">
         <v>19500</v>
       </c>
-      <c r="N90" s="18">
+      <c r="N90" s="12">
         <v>39000</v>
       </c>
-      <c r="O90" s="19" t="str">
+      <c r="O90" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P90" s="20" t="str">
+      <c r="P90" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A91" s="13">
+      <c r="A91" s="9">
         <v>46283</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D91" s="14" t="s">
+      <c r="D91" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E91" s="14" t="s">
+      <c r="E91" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F91" s="15">
+      <c r="F91" s="11">
         <v>773248259</v>
       </c>
-      <c r="G91" s="14" t="s">
+      <c r="G91" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="H91" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I91" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J91" s="14" t="s">
+      <c r="H91" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I91" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K91" s="14" t="s">
+      <c r="K91" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L91" s="14">
+      <c r="L91" s="10">
         <v>5</v>
       </c>
-      <c r="M91" s="18">
+      <c r="M91" s="12">
         <v>9000</v>
       </c>
-      <c r="N91" s="18">
+      <c r="N91" s="12">
         <v>45000</v>
       </c>
-      <c r="O91" s="19" t="str">
+      <c r="O91" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P91" s="20" t="str">
+      <c r="P91" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A92" s="13">
+      <c r="A92" s="9">
         <v>46283</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D92" s="14" t="s">
+      <c r="D92" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E92" s="14" t="s">
+      <c r="E92" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F92" s="15">
+      <c r="F92" s="11">
         <v>777802399</v>
       </c>
-      <c r="G92" s="14" t="s">
+      <c r="G92" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H92" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I92" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J92" s="14" t="s">
+      <c r="H92" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K92" s="14" t="s">
+      <c r="K92" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L92" s="14">
+      <c r="L92" s="10">
         <v>1</v>
       </c>
-      <c r="M92" s="18">
+      <c r="M92" s="12">
         <v>15500</v>
       </c>
-      <c r="N92" s="18">
+      <c r="N92" s="12">
         <v>15500</v>
       </c>
-      <c r="O92" s="19" t="str">
+      <c r="O92" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P92" s="20" t="str">
+      <c r="P92" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A93" s="13">
+      <c r="A93" s="9">
         <v>46280</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E93" s="14" t="s">
+      <c r="E93" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F93" s="15">
+      <c r="F93" s="11">
         <v>767379110</v>
       </c>
-      <c r="G93" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I93" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J93" s="14" t="s">
+      <c r="G93" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="K93" s="14" t="s">
+      <c r="K93" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="L93" s="14">
+      <c r="L93" s="10">
         <v>2</v>
       </c>
-      <c r="M93" s="18">
+      <c r="M93" s="12">
         <v>11250</v>
       </c>
-      <c r="N93" s="18">
+      <c r="N93" s="12">
         <v>22500</v>
       </c>
-      <c r="O93" s="19" t="str">
+      <c r="O93" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P93" s="20" t="str">
+      <c r="P93" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A94" s="13">
+      <c r="A94" s="9">
         <v>46282</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D94" s="14" t="s">
+      <c r="D94" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E94" s="14" t="s">
+      <c r="E94" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F94" s="15">
+      <c r="F94" s="11">
         <v>773066194</v>
       </c>
-      <c r="G94" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I94" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J94" s="14" t="s">
+      <c r="G94" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K94" s="14" t="s">
+      <c r="K94" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L94" s="14">
+      <c r="L94" s="10">
         <v>25</v>
       </c>
-      <c r="M94" s="18">
+      <c r="M94" s="12">
         <v>26000</v>
       </c>
-      <c r="N94" s="18">
+      <c r="N94" s="12">
         <v>650000</v>
       </c>
-      <c r="O94" s="19" t="str">
+      <c r="O94" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P94" s="20" t="str">
+      <c r="P94" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A95" s="13">
+      <c r="A95" s="9">
         <v>46282</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="B95" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D95" s="14" t="s">
+      <c r="D95" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E95" s="14" t="s">
+      <c r="E95" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F95" s="15">
+      <c r="F95" s="11">
         <v>774289051</v>
       </c>
-      <c r="G95" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I95" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J95" s="14" t="s">
+      <c r="G95" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K95" s="14" t="s">
+      <c r="K95" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L95" s="14">
+      <c r="L95" s="10">
         <v>25</v>
       </c>
-      <c r="M95" s="18">
+      <c r="M95" s="12">
         <v>26000</v>
       </c>
-      <c r="N95" s="18">
+      <c r="N95" s="12">
         <v>650000</v>
       </c>
-      <c r="O95" s="19" t="str">
+      <c r="O95" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P95" s="20" t="str">
+      <c r="P95" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A96" s="13">
+      <c r="A96" s="9">
         <v>46282</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D96" s="14" t="s">
+      <c r="D96" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E96" s="14" t="s">
+      <c r="E96" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="F96" s="15">
+      <c r="F96" s="11">
         <v>782442821</v>
       </c>
-      <c r="G96" s="14" t="s">
+      <c r="G96" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H96" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I96" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J96" s="14" t="s">
+      <c r="H96" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K96" s="14" t="s">
+      <c r="K96" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L96" s="14">
+      <c r="L96" s="10">
         <v>5</v>
       </c>
-      <c r="M96" s="18">
+      <c r="M96" s="12">
         <v>9000</v>
       </c>
-      <c r="N96" s="18">
+      <c r="N96" s="12">
         <v>45000</v>
       </c>
-      <c r="O96" s="19" t="str">
+      <c r="O96" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P96" s="20" t="str">
+      <c r="P96" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A97" s="13">
+      <c r="A97" s="9">
         <v>46282</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C97" s="14" t="s">
+      <c r="C97" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D97" s="14" t="s">
+      <c r="D97" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E97" s="14" t="s">
+      <c r="E97" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="F97" s="15">
+      <c r="F97" s="11">
         <v>775276149</v>
       </c>
-      <c r="G97" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H97" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I97" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J97" s="14" t="s">
+      <c r="G97" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="K97" s="14" t="s">
+      <c r="K97" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L97" s="14">
+      <c r="L97" s="10">
         <v>5</v>
       </c>
-      <c r="M97" s="18">
+      <c r="M97" s="12">
         <v>6500</v>
       </c>
-      <c r="N97" s="18">
+      <c r="N97" s="12">
         <v>32500</v>
       </c>
-      <c r="O97" s="19" t="str">
+      <c r="O97" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P97" s="20" t="str">
+      <c r="P97" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A98" s="13">
+      <c r="A98" s="9">
         <v>46282</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D98" s="14" t="s">
+      <c r="D98" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E98" s="14" t="s">
+      <c r="E98" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="F98" s="15">
+      <c r="F98" s="11">
         <v>775894237</v>
       </c>
-      <c r="G98" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H98" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I98" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J98" s="14" t="s">
+      <c r="G98" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K98" s="14" t="s">
+      <c r="K98" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L98" s="14">
+      <c r="L98" s="10">
         <v>30</v>
       </c>
-      <c r="M98" s="18">
+      <c r="M98" s="12">
         <v>9000</v>
       </c>
-      <c r="N98" s="18">
+      <c r="N98" s="12">
         <v>270000</v>
       </c>
-      <c r="O98" s="19" t="str">
+      <c r="O98" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P98" s="20" t="str">
+      <c r="P98" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A99" s="13">
+      <c r="A99" s="9">
         <v>46281</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="C99" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="14" t="s">
+      <c r="D99" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E99" s="14" t="s">
+      <c r="E99" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F99" s="15">
+      <c r="F99" s="11">
         <v>776175166</v>
       </c>
-      <c r="G99" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I99" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J99" s="14" t="s">
+      <c r="G99" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="K99" s="14" t="s">
+      <c r="K99" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L99" s="14">
+      <c r="L99" s="10">
         <v>100</v>
       </c>
-      <c r="M99" s="18">
+      <c r="M99" s="12">
         <v>26000</v>
       </c>
-      <c r="N99" s="18">
+      <c r="N99" s="12">
         <v>2600000</v>
       </c>
-      <c r="O99" s="19" t="str">
+      <c r="O99" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P99" s="20" t="str">
+      <c r="P99" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A100" s="13">
+      <c r="A100" s="9">
         <v>46281</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C100" s="14" t="s">
+      <c r="C100" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D100" s="14" t="s">
+      <c r="D100" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E100" s="14" t="s">
+      <c r="E100" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="F100" s="15">
+      <c r="F100" s="11">
         <v>776622000</v>
       </c>
-      <c r="G100" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I100" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J100" s="14" t="s">
+      <c r="G100" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="K100" s="14" t="s">
+      <c r="K100" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L100" s="14">
+      <c r="L100" s="10">
         <v>25</v>
       </c>
-      <c r="M100" s="18">
+      <c r="M100" s="12">
         <v>6500</v>
       </c>
-      <c r="N100" s="18">
+      <c r="N100" s="12">
         <v>162500</v>
       </c>
-      <c r="O100" s="19" t="str">
+      <c r="O100" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P100" s="20" t="str">
+      <c r="P100" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A101" s="13">
+      <c r="A101" s="9">
         <v>46281</v>
       </c>
-      <c r="B101" s="14" t="s">
+      <c r="B101" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C101" s="14" t="s">
+      <c r="C101" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D101" s="14" t="s">
+      <c r="D101" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E101" s="14" t="s">
+      <c r="E101" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F101" s="15">
+      <c r="F101" s="11">
         <v>775039973</v>
       </c>
-      <c r="G101" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H101" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I101" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J101" s="14" t="s">
+      <c r="G101" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="K101" s="14" t="s">
+      <c r="K101" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L101" s="14">
+      <c r="L101" s="10">
         <v>25</v>
       </c>
-      <c r="M101" s="18">
+      <c r="M101" s="12">
         <v>26000</v>
       </c>
-      <c r="N101" s="18">
+      <c r="N101" s="12">
         <v>650000</v>
       </c>
-      <c r="O101" s="19" t="str">
+      <c r="O101" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P101" s="20" t="str">
+      <c r="P101" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A102" s="13">
+      <c r="A102" s="9">
         <v>46281</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C102" s="14" t="s">
+      <c r="C102" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D102" s="14" t="s">
+      <c r="D102" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E102" s="14" t="s">
+      <c r="E102" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F102" s="15">
+      <c r="F102" s="11">
         <v>776328716</v>
       </c>
-      <c r="G102" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H102" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I102" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J102" s="14" t="s">
+      <c r="G102" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K102" s="14" t="s">
+      <c r="K102" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L102" s="14">
+      <c r="L102" s="10">
         <v>25</v>
       </c>
-      <c r="M102" s="18">
+      <c r="M102" s="12">
         <v>26000</v>
       </c>
-      <c r="N102" s="18">
+      <c r="N102" s="12">
         <v>650000</v>
       </c>
-      <c r="O102" s="19" t="str">
+      <c r="O102" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P102" s="20" t="str">
+      <c r="P102" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A103" s="13">
+      <c r="A103" s="9">
         <v>46281</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C103" s="14" t="s">
+      <c r="C103" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D103" s="14" t="s">
+      <c r="D103" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E103" s="14" t="s">
+      <c r="E103" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F103" s="15">
+      <c r="F103" s="11">
         <v>774927422</v>
       </c>
-      <c r="G103" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I103" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J103" s="14" t="s">
+      <c r="G103" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K103" s="14" t="s">
+      <c r="K103" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="L103" s="14">
+      <c r="L103" s="10">
         <v>25</v>
       </c>
-      <c r="M103" s="18">
+      <c r="M103" s="12">
         <v>26000</v>
       </c>
-      <c r="N103" s="18">
+      <c r="N103" s="12">
         <v>650000</v>
       </c>
-      <c r="O103" s="19" t="str">
+      <c r="O103" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P103" s="20" t="str">
+      <c r="P103" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A104" s="13">
+      <c r="A104" s="9">
         <v>46279</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C104" s="14" t="s">
+      <c r="C104" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D104" s="14" t="s">
+      <c r="D104" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E104" s="14" t="s">
+      <c r="E104" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F104" s="15">
+      <c r="F104" s="11">
         <v>773122246</v>
       </c>
-      <c r="G104" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H104" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I104" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J104" s="14" t="s">
+      <c r="G104" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K104" s="14" t="s">
+      <c r="K104" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L104" s="14">
+      <c r="L104" s="10">
         <v>25</v>
       </c>
-      <c r="M104" s="18">
+      <c r="M104" s="12">
         <v>9000</v>
       </c>
-      <c r="N104" s="18">
+      <c r="N104" s="12">
         <v>225000</v>
       </c>
-      <c r="O104" s="19" t="str">
+      <c r="O104" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S38</v>
       </c>
-      <c r="P104" s="20" t="str">
+      <c r="P104" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A105" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B105" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E105" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="F105" s="17">
+        <v>764970202</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J105" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="L105" s="16">
+        <v>15</v>
+      </c>
+      <c r="M105" s="18">
+        <v>12500</v>
+      </c>
+      <c r="N105" s="18">
+        <v>187500</v>
+      </c>
+      <c r="O105" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P105" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A106" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B106" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E106" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="F106" s="17">
+        <v>764970202</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J106" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="K106" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="L106" s="16">
+        <v>10</v>
+      </c>
+      <c r="M106" s="18">
+        <v>12500</v>
+      </c>
+      <c r="N106" s="18">
+        <v>125000</v>
+      </c>
+      <c r="O106" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P106" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A107" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="F107" s="17">
+        <v>773012416</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J107" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="K107" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L107" s="16">
+        <v>15</v>
+      </c>
+      <c r="M107" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N107" s="18">
+        <v>97500</v>
+      </c>
+      <c r="O107" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P107" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A108" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="F108" s="17">
+        <v>777772248</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="K108" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="L108" s="16">
+        <v>10</v>
+      </c>
+      <c r="M108" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N108" s="18">
+        <v>90000</v>
+      </c>
+      <c r="O108" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P108" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A109" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="E109" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="F109" s="17">
+        <v>773012416</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="K109" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L109" s="16">
+        <v>50</v>
+      </c>
+      <c r="M109" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N109" s="18">
+        <v>450000</v>
+      </c>
+      <c r="O109" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P109" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A110" s="15">
+        <v>46287</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E110" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F110" s="17">
+        <v>770712599</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I110" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J110" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K110" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L110" s="16">
+        <v>100</v>
+      </c>
+      <c r="M110" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N110" s="18">
+        <v>2600000</v>
+      </c>
+      <c r="O110" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P110" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A111" s="15">
+        <v>46287</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E111" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F111" s="17">
+        <v>773248259</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H111" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I111" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J111" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K111" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L111" s="16">
+        <v>1</v>
+      </c>
+      <c r="M111" s="18">
+        <v>11250</v>
+      </c>
+      <c r="N111" s="18">
+        <v>11250</v>
+      </c>
+      <c r="O111" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P111" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A112" s="15">
+        <v>46287</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E112" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F112" s="17">
+        <v>773248259</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H112" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J112" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K112" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L112" s="16">
+        <v>2</v>
+      </c>
+      <c r="M112" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N112" s="18">
+        <v>13000</v>
+      </c>
+      <c r="O112" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P112" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A113" s="15">
+        <v>46287</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E113" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F113" s="17">
+        <v>781985160</v>
+      </c>
+      <c r="G113" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="K113" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L113" s="16">
+        <v>100</v>
+      </c>
+      <c r="M113" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N113" s="18">
+        <v>2600000</v>
+      </c>
+      <c r="O113" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P113" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A114" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E114" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F114" s="17">
+        <v>773371746</v>
+      </c>
+      <c r="G114" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J114" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K114" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="L114" s="16">
+        <v>1</v>
+      </c>
+      <c r="M114" s="18">
+        <v>15500</v>
+      </c>
+      <c r="N114" s="18">
+        <v>15500</v>
+      </c>
+      <c r="O114" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P114" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A115" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B115" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E115" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F115" s="17">
+        <v>773371746</v>
+      </c>
+      <c r="G115" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="I115" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J115" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K115" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L115" s="16">
+        <v>6</v>
+      </c>
+      <c r="M115" s="18">
+        <v>6500</v>
+      </c>
+      <c r="N115" s="18">
+        <v>39000</v>
+      </c>
+      <c r="O115" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P115" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A116" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B116" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E116" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F116" s="17">
+        <v>773371746</v>
+      </c>
+      <c r="G116" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="I116" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K116" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L116" s="16">
+        <v>1</v>
+      </c>
+      <c r="M116" s="18">
+        <v>11250</v>
+      </c>
+      <c r="N116" s="18">
+        <v>11250</v>
+      </c>
+      <c r="O116" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P116" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A117" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B117" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E117" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F117" s="17">
+        <v>773371746</v>
+      </c>
+      <c r="G117" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="I117" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J117" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K117" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L117" s="16">
+        <v>51</v>
+      </c>
+      <c r="M117" s="18">
+        <v>26000</v>
+      </c>
+      <c r="N117" s="18">
+        <v>1326000</v>
+      </c>
+      <c r="O117" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P117" s="20" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>septembre</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A118" s="15">
+        <v>46288</v>
+      </c>
+      <c r="B118" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D118" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="E118" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F118" s="17">
+        <v>765956010</v>
+      </c>
+      <c r="G118" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J118" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K118" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L118" s="16">
+        <v>35</v>
+      </c>
+      <c r="M118" s="18">
+        <v>9000</v>
+      </c>
+      <c r="N118" s="18">
+        <v>315000</v>
+      </c>
+      <c r="O118" s="19" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S39</v>
+      </c>
+      <c r="P118" s="20" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>septembre</v>
       </c>
